--- a/study_tracker.xlsx
+++ b/study_tracker.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject_Metadata" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Processing_Status" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality_Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +468,11 @@
           <t>sub-01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ses-01</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>TestStudy</t>
@@ -475,15 +480,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>2026-02-01 11:23:34</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>/Users/deaniii/Developer/code/repos/qmri-neuropipe</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>/Users/deaniii/Developer/code/repos/qmri-neuropipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TestStudy</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>2026-02-01 10:34:39</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>/Users/deaniii/Developer/code/repos/qmri-neuropipe</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>/Users/deaniii/Developer/code/repos/qmri-neuropipe</t>
         </is>
@@ -500,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +574,11 @@
           <t>sub-01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ses-01</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>TestStudy</t>
@@ -554,13 +591,129 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>2026-02-01 11:23:34</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TestStudy</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-02-01 10:34:39</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Subject_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Study</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>QC_DWI_SNR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>QC_DWI_Shell_1_CNR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>QC_DWI_Motion_Rel_mm</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>QC_DWI_Outliers_Removed_Volumes</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>QC_DWI_Outliers_Removed_Pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ses-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TestStudy</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
